--- a/output/2026-09-15_19_Croazia_Požeško-slavonska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-15_19_Croazia_Požeško-slavonska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda dal 1996, webshop attivo con categoria dedicata Alati i strojevi (utensili e macchine per officina). Kompass riporta anche sede in Zagrebačka 171, Požega</t>
+          <t>Azienda dal 1996, webshop attivo con categoria dedicata Alati i strojevi (utensili e macchine per officina). Kompass riporta anche sede in Zagrebačka 171, Požega [DUPLICATO — vedi anche: 2026-09-15_02_Croazia_Pozesko-slavonska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -601,7 +601,6 @@
           <t>Diamant Artuković d.o.o.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Požega (Požeško-slavonska županija)</t>
@@ -617,7 +616,6 @@
           <t>034 273042</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Azienda reale attiva dal 1998 (Fina Info, Companywall), produzione utensili da taglio (lame/coltelli per macchine, seghe) - consumabili per lavorazioni metalliche, non officina conto terzi. Nessun sito ufficiale ne email verificabili</t>

--- a/output/2026-09-15_19_Croazia_Požeško-slavonska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-15_19_Croazia_Požeško-slavonska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -623,7 +623,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
